--- a/Manish Assignment.xlsx
+++ b/Manish Assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A760E635-9780-4985-AE13-E60EC21EA165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258A895F-4161-48EA-B969-1652ADB89E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1108,16 +1108,6 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1142,6 +1132,16 @@
     <xf numFmtId="0" fontId="18" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3250,50 +3250,50 @@
     <row r="8" spans="1:44" ht="31.5" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="59"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="59"/>
-      <c r="V8" s="59"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="59"/>
-      <c r="Z8" s="59"/>
-      <c r="AA8" s="59"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="59"/>
-      <c r="AF8" s="59"/>
-      <c r="AG8" s="59"/>
-      <c r="AH8" s="59"/>
-      <c r="AI8" s="59"/>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="59"/>
-      <c r="AL8" s="59"/>
-      <c r="AM8" s="59"/>
-      <c r="AN8" s="59"/>
-      <c r="AO8" s="59"/>
-      <c r="AP8" s="59"/>
-      <c r="AQ8" s="59"/>
-      <c r="AR8" s="60"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="73"/>
+      <c r="S8" s="73"/>
+      <c r="T8" s="73"/>
+      <c r="U8" s="73"/>
+      <c r="V8" s="73"/>
+      <c r="W8" s="73"/>
+      <c r="X8" s="73"/>
+      <c r="Y8" s="73"/>
+      <c r="Z8" s="73"/>
+      <c r="AA8" s="73"/>
+      <c r="AB8" s="73"/>
+      <c r="AC8" s="73"/>
+      <c r="AD8" s="73"/>
+      <c r="AE8" s="73"/>
+      <c r="AF8" s="73"/>
+      <c r="AG8" s="73"/>
+      <c r="AH8" s="73"/>
+      <c r="AI8" s="73"/>
+      <c r="AJ8" s="73"/>
+      <c r="AK8" s="73"/>
+      <c r="AL8" s="73"/>
+      <c r="AM8" s="73"/>
+      <c r="AN8" s="73"/>
+      <c r="AO8" s="73"/>
+      <c r="AP8" s="73"/>
+      <c r="AQ8" s="73"/>
+      <c r="AR8" s="74"/>
     </row>
     <row r="9" spans="1:44" ht="14.25" customHeight="1">
       <c r="A9" s="11"/>
@@ -5124,50 +5124,50 @@
     <row r="27" spans="1:44" ht="52.5" customHeight="1" thickBot="1">
       <c r="A27" s="37"/>
       <c r="B27" s="38"/>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="62"/>
-      <c r="S27" s="62"/>
-      <c r="T27" s="62"/>
-      <c r="U27" s="62"/>
-      <c r="V27" s="62"/>
-      <c r="W27" s="62"/>
-      <c r="X27" s="62"/>
-      <c r="Y27" s="62"/>
-      <c r="Z27" s="62"/>
-      <c r="AA27" s="62"/>
-      <c r="AB27" s="62"/>
-      <c r="AC27" s="62"/>
-      <c r="AD27" s="62"/>
-      <c r="AE27" s="62"/>
-      <c r="AF27" s="62"/>
-      <c r="AG27" s="62"/>
-      <c r="AH27" s="62"/>
-      <c r="AI27" s="62"/>
-      <c r="AJ27" s="62"/>
-      <c r="AK27" s="62"/>
-      <c r="AL27" s="62"/>
-      <c r="AM27" s="62"/>
-      <c r="AN27" s="62"/>
-      <c r="AO27" s="62"/>
-      <c r="AP27" s="62"/>
-      <c r="AQ27" s="62"/>
-      <c r="AR27" s="63"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="76"/>
+      <c r="Q27" s="76"/>
+      <c r="R27" s="76"/>
+      <c r="S27" s="76"/>
+      <c r="T27" s="76"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="76"/>
+      <c r="X27" s="76"/>
+      <c r="Y27" s="76"/>
+      <c r="Z27" s="76"/>
+      <c r="AA27" s="76"/>
+      <c r="AB27" s="76"/>
+      <c r="AC27" s="76"/>
+      <c r="AD27" s="76"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="76"/>
+      <c r="AJ27" s="76"/>
+      <c r="AK27" s="76"/>
+      <c r="AL27" s="76"/>
+      <c r="AM27" s="76"/>
+      <c r="AN27" s="76"/>
+      <c r="AO27" s="76"/>
+      <c r="AP27" s="76"/>
+      <c r="AQ27" s="76"/>
+      <c r="AR27" s="77"/>
     </row>
     <row r="28" spans="1:44" ht="14.25" customHeight="1" thickBot="1">
       <c r="A28" s="37"/>
@@ -6358,50 +6358,50 @@
     <row r="38" spans="1:44" ht="14.25" customHeight="1">
       <c r="A38" s="37"/>
       <c r="B38" s="38"/>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="62"/>
-      <c r="O38" s="62"/>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="62"/>
-      <c r="T38" s="62"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="62"/>
-      <c r="W38" s="62"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="62"/>
-      <c r="AA38" s="62"/>
-      <c r="AB38" s="62"/>
-      <c r="AC38" s="62"/>
-      <c r="AD38" s="62"/>
-      <c r="AE38" s="62"/>
-      <c r="AF38" s="62"/>
-      <c r="AG38" s="62"/>
-      <c r="AH38" s="62"/>
-      <c r="AI38" s="62"/>
-      <c r="AJ38" s="62"/>
-      <c r="AK38" s="62"/>
-      <c r="AL38" s="62"/>
-      <c r="AM38" s="62"/>
-      <c r="AN38" s="62"/>
-      <c r="AO38" s="62"/>
-      <c r="AP38" s="62"/>
-      <c r="AQ38" s="62"/>
-      <c r="AR38" s="63"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="76"/>
+      <c r="S38" s="76"/>
+      <c r="T38" s="76"/>
+      <c r="U38" s="76"/>
+      <c r="V38" s="76"/>
+      <c r="W38" s="76"/>
+      <c r="X38" s="76"/>
+      <c r="Y38" s="76"/>
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="76"/>
+      <c r="AB38" s="76"/>
+      <c r="AC38" s="76"/>
+      <c r="AD38" s="76"/>
+      <c r="AE38" s="76"/>
+      <c r="AF38" s="76"/>
+      <c r="AG38" s="76"/>
+      <c r="AH38" s="76"/>
+      <c r="AI38" s="76"/>
+      <c r="AJ38" s="76"/>
+      <c r="AK38" s="76"/>
+      <c r="AL38" s="76"/>
+      <c r="AM38" s="76"/>
+      <c r="AN38" s="76"/>
+      <c r="AO38" s="76"/>
+      <c r="AP38" s="76"/>
+      <c r="AQ38" s="76"/>
+      <c r="AR38" s="77"/>
     </row>
     <row r="39" spans="1:44" ht="14.25" customHeight="1">
       <c r="A39" s="37"/>
@@ -7592,50 +7592,50 @@
     <row r="49" spans="1:44" ht="14.25" customHeight="1">
       <c r="A49" s="37"/>
       <c r="B49" s="38"/>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="62"/>
-      <c r="K49" s="62"/>
-      <c r="L49" s="62"/>
-      <c r="M49" s="62"/>
-      <c r="N49" s="62"/>
-      <c r="O49" s="62"/>
-      <c r="P49" s="62"/>
-      <c r="Q49" s="62"/>
-      <c r="R49" s="62"/>
-      <c r="S49" s="62"/>
-      <c r="T49" s="62"/>
-      <c r="U49" s="62"/>
-      <c r="V49" s="62"/>
-      <c r="W49" s="62"/>
-      <c r="X49" s="62"/>
-      <c r="Y49" s="62"/>
-      <c r="Z49" s="62"/>
-      <c r="AA49" s="62"/>
-      <c r="AB49" s="62"/>
-      <c r="AC49" s="62"/>
-      <c r="AD49" s="62"/>
-      <c r="AE49" s="62"/>
-      <c r="AF49" s="62"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
-      <c r="AJ49" s="62"/>
-      <c r="AK49" s="62"/>
-      <c r="AL49" s="62"/>
-      <c r="AM49" s="62"/>
-      <c r="AN49" s="62"/>
-      <c r="AO49" s="62"/>
-      <c r="AP49" s="62"/>
-      <c r="AQ49" s="62"/>
-      <c r="AR49" s="63"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76"/>
+      <c r="J49" s="76"/>
+      <c r="K49" s="76"/>
+      <c r="L49" s="76"/>
+      <c r="M49" s="76"/>
+      <c r="N49" s="76"/>
+      <c r="O49" s="76"/>
+      <c r="P49" s="76"/>
+      <c r="Q49" s="76"/>
+      <c r="R49" s="76"/>
+      <c r="S49" s="76"/>
+      <c r="T49" s="76"/>
+      <c r="U49" s="76"/>
+      <c r="V49" s="76"/>
+      <c r="W49" s="76"/>
+      <c r="X49" s="76"/>
+      <c r="Y49" s="76"/>
+      <c r="Z49" s="76"/>
+      <c r="AA49" s="76"/>
+      <c r="AB49" s="76"/>
+      <c r="AC49" s="76"/>
+      <c r="AD49" s="76"/>
+      <c r="AE49" s="76"/>
+      <c r="AF49" s="76"/>
+      <c r="AG49" s="76"/>
+      <c r="AH49" s="76"/>
+      <c r="AI49" s="76"/>
+      <c r="AJ49" s="76"/>
+      <c r="AK49" s="76"/>
+      <c r="AL49" s="76"/>
+      <c r="AM49" s="76"/>
+      <c r="AN49" s="76"/>
+      <c r="AO49" s="76"/>
+      <c r="AP49" s="76"/>
+      <c r="AQ49" s="76"/>
+      <c r="AR49" s="77"/>
     </row>
     <row r="50" spans="1:44" ht="14.25" customHeight="1">
       <c r="A50" s="37"/>
@@ -8826,50 +8826,50 @@
     <row r="60" spans="1:44" ht="14.25" customHeight="1">
       <c r="A60" s="37"/>
       <c r="B60" s="38"/>
-      <c r="C60" s="61" t="s">
+      <c r="C60" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="D60" s="62"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="62"/>
-      <c r="G60" s="62"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="62"/>
-      <c r="J60" s="62"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="62"/>
-      <c r="M60" s="62"/>
-      <c r="N60" s="62"/>
-      <c r="O60" s="62"/>
-      <c r="P60" s="62"/>
-      <c r="Q60" s="62"/>
-      <c r="R60" s="62"/>
-      <c r="S60" s="62"/>
-      <c r="T60" s="62"/>
-      <c r="U60" s="62"/>
-      <c r="V60" s="62"/>
-      <c r="W60" s="62"/>
-      <c r="X60" s="62"/>
-      <c r="Y60" s="62"/>
-      <c r="Z60" s="62"/>
-      <c r="AA60" s="62"/>
-      <c r="AB60" s="62"/>
-      <c r="AC60" s="62"/>
-      <c r="AD60" s="62"/>
-      <c r="AE60" s="62"/>
-      <c r="AF60" s="62"/>
-      <c r="AG60" s="62"/>
-      <c r="AH60" s="62"/>
-      <c r="AI60" s="62"/>
-      <c r="AJ60" s="62"/>
-      <c r="AK60" s="62"/>
-      <c r="AL60" s="62"/>
-      <c r="AM60" s="62"/>
-      <c r="AN60" s="62"/>
-      <c r="AO60" s="62"/>
-      <c r="AP60" s="62"/>
-      <c r="AQ60" s="62"/>
-      <c r="AR60" s="63"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="76"/>
+      <c r="L60" s="76"/>
+      <c r="M60" s="76"/>
+      <c r="N60" s="76"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="76"/>
+      <c r="Q60" s="76"/>
+      <c r="R60" s="76"/>
+      <c r="S60" s="76"/>
+      <c r="T60" s="76"/>
+      <c r="U60" s="76"/>
+      <c r="V60" s="76"/>
+      <c r="W60" s="76"/>
+      <c r="X60" s="76"/>
+      <c r="Y60" s="76"/>
+      <c r="Z60" s="76"/>
+      <c r="AA60" s="76"/>
+      <c r="AB60" s="76"/>
+      <c r="AC60" s="76"/>
+      <c r="AD60" s="76"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="76"/>
+      <c r="AJ60" s="76"/>
+      <c r="AK60" s="76"/>
+      <c r="AL60" s="76"/>
+      <c r="AM60" s="76"/>
+      <c r="AN60" s="76"/>
+      <c r="AO60" s="76"/>
+      <c r="AP60" s="76"/>
+      <c r="AQ60" s="76"/>
+      <c r="AR60" s="77"/>
     </row>
     <row r="61" spans="1:44" ht="14.25" customHeight="1">
       <c r="A61" s="37"/>
@@ -19960,11 +19960,11 @@
       <c r="Z1" s="46"/>
     </row>
     <row r="2" spans="1:26" ht="27.6">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="66"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
@@ -19992,25 +19992,25 @@
       <c r="Z2" s="46"/>
     </row>
     <row r="3" spans="1:26" ht="27" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="69"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="63"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="46"/>
       <c r="R3" s="46"/>
@@ -20450,25 +20450,25 @@
       <c r="Z17" s="46"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="73"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="67"/>
       <c r="H18" s="46"/>
-      <c r="I18" s="77" t="s">
+      <c r="I18" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="73"/>
+      <c r="J18" s="66"/>
+      <c r="K18" s="66"/>
+      <c r="L18" s="66"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="67"/>
       <c r="P18" s="46"/>
       <c r="Q18" s="46"/>
       <c r="R18" s="46"/>
@@ -20482,21 +20482,21 @@
       <c r="Z18" s="46"/>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A19" s="74"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="76"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="46"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="75"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="75"/>
-      <c r="N19" s="75"/>
-      <c r="O19" s="76"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="70"/>
       <c r="P19" s="46"/>
       <c r="Q19" s="46"/>
       <c r="R19" s="46"/>
